--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4734" uniqueCount="3223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4748" uniqueCount="3231">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4561,7 +4561,7 @@
     <t>0709</t>
   </si>
   <si>
-    <t>Entéro-IRM</t>
+    <t>Colo-IRM et entéro-IRM</t>
   </si>
   <si>
     <t>0710</t>
@@ -6256,7 +6256,7 @@
     <t>Visite à domicile</t>
   </si>
   <si>
-    <t>L'acte "visite à domicile" permet de caractériser la façon dont est réalisée une consultation par un médecin. Une consultation peut être réalisée en présentiel, en téléconsultation ou en visite à domicile. Intervention d'un professionnel de santé, au domicile d'un patient pour lui prodiguer des soins ou réaliser un suivi médical pour les patients ayant des difficultés à se déplacer, permettent d'assurer une continuité des soins dans un environnement familier pour le patient</t>
+    <t>Intervention d'un professionnel de santé au domicile d'un patient ou d'un usager pour assurer une continuité des soins et/ou de la prise en charge, de l'accompagnement</t>
   </si>
   <si>
     <t>0990</t>
@@ -7249,7 +7249,7 @@
     <t>1119</t>
   </si>
   <si>
-    <t>Chirurgie du défilé cervico-thoracique</t>
+    <t>Chirurgie du défilé cervico thoraco brachial</t>
   </si>
   <si>
     <t>Décompression vasculaire et neurologique de l'espace costo-claviculaire</t>
@@ -7480,7 +7480,7 @@
     <t>1151</t>
   </si>
   <si>
-    <t>Chirurgie oncologique de l'oesophage ou de la jonction gastro-oesophagienne</t>
+    <t>Chirurgie carcinologique de l'oesophage ou de la jonction gastro-oesophagienne</t>
   </si>
   <si>
     <t>Chirurgie qui consiste en l'ablation complète ou partielle de l'oesophage en fonction de la localisation de la tumeur et de son stade</t>
@@ -7573,9 +7573,6 @@
     <t>1166</t>
   </si>
   <si>
-    <t>Colo-IRM et entéro-IRM</t>
-  </si>
-  <si>
     <t>1167</t>
   </si>
   <si>
@@ -7699,9 +7696,6 @@
     <t>Echographie clinique ciblée</t>
   </si>
   <si>
-    <t>Technique d'imagerie par échographie de manière ciblée (en anglais "Point-of-Care Ultrasound" ou POCUS) pour répondre à des questions cliniques spécifiques et urgentes, plutôt que pour effectuer une évaluation complète comme le ferait un radiologue, elle se distingue par sa rapidité, sa précision pour des questions spécifiques, et son utilisation directement par les professionnels de santé impliqués dans les soins immédiats du patient</t>
-  </si>
-  <si>
     <t>1187</t>
   </si>
   <si>
@@ -8308,7 +8302,7 @@
     <t>1279</t>
   </si>
   <si>
-    <t>Télésurveillance des prothèses rythmiques</t>
+    <t>Télésurveillance médicale de l'arythmie cardiaque</t>
   </si>
   <si>
     <t>1280</t>
@@ -9574,13 +9568,13 @@
     <t>1464</t>
   </si>
   <si>
-    <t>Certificats médicaux pour le sport de haut niveau (SHN)</t>
+    <t>Délivrance de certificats médicaux pour le sport de haut niveau (SHN)</t>
   </si>
   <si>
     <t>1465</t>
   </si>
   <si>
-    <t>Certificats spécifiques pour les sportifs en situation de Handicap</t>
+    <t>Délivrance de certificats spécifiques pour les sportifs en situation de Handicap</t>
   </si>
   <si>
     <t>1466</t>
@@ -9683,6 +9677,36 @@
   </si>
   <si>
     <t>Cryothérapie compressive</t>
+  </si>
+  <si>
+    <t>1483</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance cardiaque</t>
+  </si>
+  <si>
+    <t>1484</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance rénale</t>
+  </si>
+  <si>
+    <t>1485</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance respiratoire</t>
+  </si>
+  <si>
+    <t>1486</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale du diabète</t>
+  </si>
+  <si>
+    <t>1487</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale en oncologie</t>
   </si>
 </sst>
 </file>
@@ -10056,7 +10080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1482"/>
+  <dimension ref="A1:D1487"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -24373,7 +24397,7 @@
         <v>2518</v>
       </c>
       <c r="C1167" t="s" s="2">
-        <v>2519</v>
+        <v>1515</v>
       </c>
       <c r="D1167" s="2"/>
     </row>
@@ -24382,13 +24406,13 @@
         <v>49</v>
       </c>
       <c r="B1168" t="s" s="2">
+        <v>2519</v>
+      </c>
+      <c r="C1168" t="s" s="2">
         <v>2520</v>
       </c>
-      <c r="C1168" t="s" s="2">
+      <c r="D1168" t="s" s="2">
         <v>2521</v>
-      </c>
-      <c r="D1168" t="s" s="2">
-        <v>2522</v>
       </c>
     </row>
     <row r="1169">
@@ -24396,10 +24420,10 @@
         <v>49</v>
       </c>
       <c r="B1169" t="s" s="2">
+        <v>2522</v>
+      </c>
+      <c r="C1169" t="s" s="2">
         <v>2523</v>
-      </c>
-      <c r="C1169" t="s" s="2">
-        <v>2524</v>
       </c>
       <c r="D1169" s="2"/>
     </row>
@@ -24408,10 +24432,10 @@
         <v>49</v>
       </c>
       <c r="B1170" t="s" s="2">
+        <v>2524</v>
+      </c>
+      <c r="C1170" t="s" s="2">
         <v>2525</v>
-      </c>
-      <c r="C1170" t="s" s="2">
-        <v>2526</v>
       </c>
       <c r="D1170" s="2"/>
     </row>
@@ -24420,10 +24444,10 @@
         <v>49</v>
       </c>
       <c r="B1171" t="s" s="2">
+        <v>2526</v>
+      </c>
+      <c r="C1171" t="s" s="2">
         <v>2527</v>
-      </c>
-      <c r="C1171" t="s" s="2">
-        <v>2528</v>
       </c>
       <c r="D1171" s="2"/>
     </row>
@@ -24432,10 +24456,10 @@
         <v>49</v>
       </c>
       <c r="B1172" t="s" s="2">
+        <v>2528</v>
+      </c>
+      <c r="C1172" t="s" s="2">
         <v>2529</v>
-      </c>
-      <c r="C1172" t="s" s="2">
-        <v>2530</v>
       </c>
       <c r="D1172" s="2"/>
     </row>
@@ -24444,10 +24468,10 @@
         <v>49</v>
       </c>
       <c r="B1173" t="s" s="2">
+        <v>2530</v>
+      </c>
+      <c r="C1173" t="s" s="2">
         <v>2531</v>
-      </c>
-      <c r="C1173" t="s" s="2">
-        <v>2532</v>
       </c>
       <c r="D1173" s="2"/>
     </row>
@@ -24456,10 +24480,10 @@
         <v>49</v>
       </c>
       <c r="B1174" t="s" s="2">
+        <v>2532</v>
+      </c>
+      <c r="C1174" t="s" s="2">
         <v>2533</v>
-      </c>
-      <c r="C1174" t="s" s="2">
-        <v>2534</v>
       </c>
       <c r="D1174" s="2"/>
     </row>
@@ -24468,10 +24492,10 @@
         <v>49</v>
       </c>
       <c r="B1175" t="s" s="2">
+        <v>2534</v>
+      </c>
+      <c r="C1175" t="s" s="2">
         <v>2535</v>
-      </c>
-      <c r="C1175" t="s" s="2">
-        <v>2536</v>
       </c>
       <c r="D1175" s="2"/>
     </row>
@@ -24480,10 +24504,10 @@
         <v>49</v>
       </c>
       <c r="B1176" t="s" s="2">
+        <v>2536</v>
+      </c>
+      <c r="C1176" t="s" s="2">
         <v>2537</v>
-      </c>
-      <c r="C1176" t="s" s="2">
-        <v>2538</v>
       </c>
       <c r="D1176" s="2"/>
     </row>
@@ -24492,10 +24516,10 @@
         <v>49</v>
       </c>
       <c r="B1177" t="s" s="2">
+        <v>2538</v>
+      </c>
+      <c r="C1177" t="s" s="2">
         <v>2539</v>
-      </c>
-      <c r="C1177" t="s" s="2">
-        <v>2540</v>
       </c>
       <c r="D1177" s="2"/>
     </row>
@@ -24504,10 +24528,10 @@
         <v>49</v>
       </c>
       <c r="B1178" t="s" s="2">
+        <v>2540</v>
+      </c>
+      <c r="C1178" t="s" s="2">
         <v>2541</v>
-      </c>
-      <c r="C1178" t="s" s="2">
-        <v>2542</v>
       </c>
       <c r="D1178" s="2"/>
     </row>
@@ -24516,10 +24540,10 @@
         <v>49</v>
       </c>
       <c r="B1179" t="s" s="2">
+        <v>2542</v>
+      </c>
+      <c r="C1179" t="s" s="2">
         <v>2543</v>
-      </c>
-      <c r="C1179" t="s" s="2">
-        <v>2544</v>
       </c>
       <c r="D1179" s="2"/>
     </row>
@@ -24528,10 +24552,10 @@
         <v>49</v>
       </c>
       <c r="B1180" t="s" s="2">
+        <v>2544</v>
+      </c>
+      <c r="C1180" t="s" s="2">
         <v>2545</v>
-      </c>
-      <c r="C1180" t="s" s="2">
-        <v>2546</v>
       </c>
       <c r="D1180" s="2"/>
     </row>
@@ -24540,10 +24564,10 @@
         <v>49</v>
       </c>
       <c r="B1181" t="s" s="2">
+        <v>2546</v>
+      </c>
+      <c r="C1181" t="s" s="2">
         <v>2547</v>
-      </c>
-      <c r="C1181" t="s" s="2">
-        <v>2548</v>
       </c>
       <c r="D1181" s="2"/>
     </row>
@@ -24552,13 +24576,13 @@
         <v>49</v>
       </c>
       <c r="B1182" t="s" s="2">
+        <v>2548</v>
+      </c>
+      <c r="C1182" t="s" s="2">
         <v>2549</v>
       </c>
-      <c r="C1182" t="s" s="2">
+      <c r="D1182" t="s" s="2">
         <v>2550</v>
-      </c>
-      <c r="D1182" t="s" s="2">
-        <v>2551</v>
       </c>
     </row>
     <row r="1183">
@@ -24566,10 +24590,10 @@
         <v>49</v>
       </c>
       <c r="B1183" t="s" s="2">
+        <v>2551</v>
+      </c>
+      <c r="C1183" t="s" s="2">
         <v>2552</v>
-      </c>
-      <c r="C1183" t="s" s="2">
-        <v>2553</v>
       </c>
       <c r="D1183" s="2"/>
     </row>
@@ -24578,10 +24602,10 @@
         <v>49</v>
       </c>
       <c r="B1184" t="s" s="2">
+        <v>2553</v>
+      </c>
+      <c r="C1184" t="s" s="2">
         <v>2554</v>
-      </c>
-      <c r="C1184" t="s" s="2">
-        <v>2555</v>
       </c>
       <c r="D1184" s="2"/>
     </row>
@@ -24590,10 +24614,10 @@
         <v>49</v>
       </c>
       <c r="B1185" t="s" s="2">
+        <v>2555</v>
+      </c>
+      <c r="C1185" t="s" s="2">
         <v>2556</v>
-      </c>
-      <c r="C1185" t="s" s="2">
-        <v>2557</v>
       </c>
       <c r="D1185" s="2"/>
     </row>
@@ -24602,7 +24626,7 @@
         <v>49</v>
       </c>
       <c r="B1186" t="s" s="2">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="C1186" t="s" s="2">
         <v>1969</v>
@@ -24614,27 +24638,25 @@
         <v>49</v>
       </c>
       <c r="B1187" t="s" s="2">
+        <v>2558</v>
+      </c>
+      <c r="C1187" t="s" s="2">
         <v>2559</v>
       </c>
-      <c r="C1187" t="s" s="2">
-        <v>2560</v>
-      </c>
-      <c r="D1187" t="s" s="2">
-        <v>2561</v>
-      </c>
+      <c r="D1187" s="2"/>
     </row>
     <row r="1188">
       <c r="A1188" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1188" t="s" s="2">
+        <v>2560</v>
+      </c>
+      <c r="C1188" t="s" s="2">
+        <v>2561</v>
+      </c>
+      <c r="D1188" t="s" s="2">
         <v>2562</v>
-      </c>
-      <c r="C1188" t="s" s="2">
-        <v>2563</v>
-      </c>
-      <c r="D1188" t="s" s="2">
-        <v>2564</v>
       </c>
     </row>
     <row r="1189">
@@ -24642,10 +24664,10 @@
         <v>49</v>
       </c>
       <c r="B1189" t="s" s="2">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="C1189" t="s" s="2">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="D1189" s="2"/>
     </row>
@@ -24654,10 +24676,10 @@
         <v>49</v>
       </c>
       <c r="B1190" t="s" s="2">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="C1190" t="s" s="2">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="D1190" s="2"/>
     </row>
@@ -24666,10 +24688,10 @@
         <v>49</v>
       </c>
       <c r="B1191" t="s" s="2">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="C1191" t="s" s="2">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="D1191" s="2"/>
     </row>
@@ -24678,10 +24700,10 @@
         <v>49</v>
       </c>
       <c r="B1192" t="s" s="2">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="C1192" t="s" s="2">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="D1192" s="2"/>
     </row>
@@ -24690,10 +24712,10 @@
         <v>49</v>
       </c>
       <c r="B1193" t="s" s="2">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="C1193" t="s" s="2">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="D1193" s="2"/>
     </row>
@@ -24702,10 +24724,10 @@
         <v>49</v>
       </c>
       <c r="B1194" t="s" s="2">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="C1194" t="s" s="2">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="D1194" s="2"/>
     </row>
@@ -24714,10 +24736,10 @@
         <v>49</v>
       </c>
       <c r="B1195" t="s" s="2">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="C1195" t="s" s="2">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="D1195" s="2"/>
     </row>
@@ -24726,10 +24748,10 @@
         <v>49</v>
       </c>
       <c r="B1196" t="s" s="2">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="C1196" t="s" s="2">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="D1196" s="2"/>
     </row>
@@ -24738,13 +24760,13 @@
         <v>49</v>
       </c>
       <c r="B1197" t="s" s="2">
+        <v>2579</v>
+      </c>
+      <c r="C1197" t="s" s="2">
+        <v>2580</v>
+      </c>
+      <c r="D1197" t="s" s="2">
         <v>2581</v>
-      </c>
-      <c r="C1197" t="s" s="2">
-        <v>2582</v>
-      </c>
-      <c r="D1197" t="s" s="2">
-        <v>2583</v>
       </c>
     </row>
     <row r="1198">
@@ -24752,13 +24774,13 @@
         <v>49</v>
       </c>
       <c r="B1198" t="s" s="2">
+        <v>2582</v>
+      </c>
+      <c r="C1198" t="s" s="2">
+        <v>2583</v>
+      </c>
+      <c r="D1198" t="s" s="2">
         <v>2584</v>
-      </c>
-      <c r="C1198" t="s" s="2">
-        <v>2585</v>
-      </c>
-      <c r="D1198" t="s" s="2">
-        <v>2586</v>
       </c>
     </row>
     <row r="1199">
@@ -24766,13 +24788,13 @@
         <v>49</v>
       </c>
       <c r="B1199" t="s" s="2">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="C1199" t="s" s="2">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="D1199" t="s" s="2">
-        <v>2586</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="1200">
@@ -24780,13 +24802,13 @@
         <v>49</v>
       </c>
       <c r="B1200" t="s" s="2">
+        <v>2587</v>
+      </c>
+      <c r="C1200" t="s" s="2">
+        <v>2588</v>
+      </c>
+      <c r="D1200" t="s" s="2">
         <v>2589</v>
-      </c>
-      <c r="C1200" t="s" s="2">
-        <v>2590</v>
-      </c>
-      <c r="D1200" t="s" s="2">
-        <v>2591</v>
       </c>
     </row>
     <row r="1201">
@@ -24794,10 +24816,10 @@
         <v>49</v>
       </c>
       <c r="B1201" t="s" s="2">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="C1201" t="s" s="2">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="D1201" s="2"/>
     </row>
@@ -24806,10 +24828,10 @@
         <v>49</v>
       </c>
       <c r="B1202" t="s" s="2">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="C1202" t="s" s="2">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="D1202" s="2"/>
     </row>
@@ -24818,10 +24840,10 @@
         <v>49</v>
       </c>
       <c r="B1203" t="s" s="2">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="C1203" t="s" s="2">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="D1203" s="2"/>
     </row>
@@ -24830,10 +24852,10 @@
         <v>49</v>
       </c>
       <c r="B1204" t="s" s="2">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="C1204" t="s" s="2">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="D1204" s="2"/>
     </row>
@@ -24842,10 +24864,10 @@
         <v>49</v>
       </c>
       <c r="B1205" t="s" s="2">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="C1205" t="s" s="2">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="D1205" s="2"/>
     </row>
@@ -24854,10 +24876,10 @@
         <v>49</v>
       </c>
       <c r="B1206" t="s" s="2">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="C1206" t="s" s="2">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="D1206" s="2"/>
     </row>
@@ -24866,10 +24888,10 @@
         <v>49</v>
       </c>
       <c r="B1207" t="s" s="2">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="C1207" t="s" s="2">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="D1207" s="2"/>
     </row>
@@ -24878,13 +24900,13 @@
         <v>49</v>
       </c>
       <c r="B1208" t="s" s="2">
+        <v>2604</v>
+      </c>
+      <c r="C1208" t="s" s="2">
+        <v>2605</v>
+      </c>
+      <c r="D1208" t="s" s="2">
         <v>2606</v>
-      </c>
-      <c r="C1208" t="s" s="2">
-        <v>2607</v>
-      </c>
-      <c r="D1208" t="s" s="2">
-        <v>2608</v>
       </c>
     </row>
     <row r="1209">
@@ -24892,10 +24914,10 @@
         <v>49</v>
       </c>
       <c r="B1209" t="s" s="2">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="C1209" t="s" s="2">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="D1209" s="2"/>
     </row>
@@ -24904,10 +24926,10 @@
         <v>49</v>
       </c>
       <c r="B1210" t="s" s="2">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C1210" t="s" s="2">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="D1210" s="2"/>
     </row>
@@ -24916,10 +24938,10 @@
         <v>49</v>
       </c>
       <c r="B1211" t="s" s="2">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="C1211" t="s" s="2">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="D1211" s="2"/>
     </row>
@@ -24928,10 +24950,10 @@
         <v>49</v>
       </c>
       <c r="B1212" t="s" s="2">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="C1212" t="s" s="2">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="D1212" s="2"/>
     </row>
@@ -24940,10 +24962,10 @@
         <v>49</v>
       </c>
       <c r="B1213" t="s" s="2">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="C1213" t="s" s="2">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D1213" s="2"/>
     </row>
@@ -24952,10 +24974,10 @@
         <v>49</v>
       </c>
       <c r="B1214" t="s" s="2">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="C1214" t="s" s="2">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="D1214" s="2"/>
     </row>
@@ -24964,13 +24986,13 @@
         <v>49</v>
       </c>
       <c r="B1215" t="s" s="2">
+        <v>2619</v>
+      </c>
+      <c r="C1215" t="s" s="2">
+        <v>2620</v>
+      </c>
+      <c r="D1215" t="s" s="2">
         <v>2621</v>
-      </c>
-      <c r="C1215" t="s" s="2">
-        <v>2622</v>
-      </c>
-      <c r="D1215" t="s" s="2">
-        <v>2623</v>
       </c>
     </row>
     <row r="1216">
@@ -24978,10 +25000,10 @@
         <v>49</v>
       </c>
       <c r="B1216" t="s" s="2">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="C1216" t="s" s="2">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="D1216" s="2"/>
     </row>
@@ -24990,10 +25012,10 @@
         <v>49</v>
       </c>
       <c r="B1217" t="s" s="2">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="C1217" t="s" s="2">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="D1217" s="2"/>
     </row>
@@ -25002,10 +25024,10 @@
         <v>49</v>
       </c>
       <c r="B1218" t="s" s="2">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="C1218" t="s" s="2">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="D1218" s="2"/>
     </row>
@@ -25014,10 +25036,10 @@
         <v>49</v>
       </c>
       <c r="B1219" t="s" s="2">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="C1219" t="s" s="2">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="D1219" s="2"/>
     </row>
@@ -25026,10 +25048,10 @@
         <v>49</v>
       </c>
       <c r="B1220" t="s" s="2">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="C1220" t="s" s="2">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="D1220" s="2"/>
     </row>
@@ -25038,10 +25060,10 @@
         <v>49</v>
       </c>
       <c r="B1221" t="s" s="2">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="C1221" t="s" s="2">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="D1221" s="2"/>
     </row>
@@ -25050,10 +25072,10 @@
         <v>49</v>
       </c>
       <c r="B1222" t="s" s="2">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="C1222" t="s" s="2">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="D1222" s="2"/>
     </row>
@@ -25062,10 +25084,10 @@
         <v>49</v>
       </c>
       <c r="B1223" t="s" s="2">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="C1223" t="s" s="2">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="D1223" s="2"/>
     </row>
@@ -25074,10 +25096,10 @@
         <v>49</v>
       </c>
       <c r="B1224" t="s" s="2">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="C1224" t="s" s="2">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="D1224" s="2"/>
     </row>
@@ -25086,10 +25108,10 @@
         <v>49</v>
       </c>
       <c r="B1225" t="s" s="2">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="C1225" t="s" s="2">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="D1225" s="2"/>
     </row>
@@ -25098,10 +25120,10 @@
         <v>49</v>
       </c>
       <c r="B1226" t="s" s="2">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="C1226" t="s" s="2">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="D1226" s="2"/>
     </row>
@@ -25110,10 +25132,10 @@
         <v>49</v>
       </c>
       <c r="B1227" t="s" s="2">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="C1227" t="s" s="2">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="D1227" s="2"/>
     </row>
@@ -25122,10 +25144,10 @@
         <v>49</v>
       </c>
       <c r="B1228" t="s" s="2">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="C1228" t="s" s="2">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="D1228" s="2"/>
     </row>
@@ -25134,10 +25156,10 @@
         <v>49</v>
       </c>
       <c r="B1229" t="s" s="2">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C1229" t="s" s="2">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="D1229" s="2"/>
     </row>
@@ -25146,10 +25168,10 @@
         <v>49</v>
       </c>
       <c r="B1230" t="s" s="2">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="C1230" t="s" s="2">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="D1230" s="2"/>
     </row>
@@ -25158,10 +25180,10 @@
         <v>49</v>
       </c>
       <c r="B1231" t="s" s="2">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="C1231" t="s" s="2">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="D1231" s="2"/>
     </row>
@@ -25170,10 +25192,10 @@
         <v>49</v>
       </c>
       <c r="B1232" t="s" s="2">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="C1232" t="s" s="2">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="D1232" s="2"/>
     </row>
@@ -25182,10 +25204,10 @@
         <v>49</v>
       </c>
       <c r="B1233" t="s" s="2">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="C1233" t="s" s="2">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="D1233" s="2"/>
     </row>
@@ -25194,10 +25216,10 @@
         <v>49</v>
       </c>
       <c r="B1234" t="s" s="2">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C1234" t="s" s="2">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="D1234" s="2"/>
     </row>
@@ -25206,10 +25228,10 @@
         <v>49</v>
       </c>
       <c r="B1235" t="s" s="2">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C1235" t="s" s="2">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="D1235" s="2"/>
     </row>
@@ -25218,10 +25240,10 @@
         <v>49</v>
       </c>
       <c r="B1236" t="s" s="2">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C1236" t="s" s="2">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="D1236" s="2"/>
     </row>
@@ -25230,10 +25252,10 @@
         <v>49</v>
       </c>
       <c r="B1237" t="s" s="2">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="C1237" t="s" s="2">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="D1237" s="2"/>
     </row>
@@ -25242,10 +25264,10 @@
         <v>49</v>
       </c>
       <c r="B1238" t="s" s="2">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="C1238" t="s" s="2">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="D1238" s="2"/>
     </row>
@@ -25254,10 +25276,10 @@
         <v>49</v>
       </c>
       <c r="B1239" t="s" s="2">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="C1239" t="s" s="2">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="D1239" s="2"/>
     </row>
@@ -25266,10 +25288,10 @@
         <v>49</v>
       </c>
       <c r="B1240" t="s" s="2">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="C1240" t="s" s="2">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="D1240" s="2"/>
     </row>
@@ -25278,10 +25300,10 @@
         <v>49</v>
       </c>
       <c r="B1241" t="s" s="2">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="C1241" t="s" s="2">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="D1241" s="2"/>
     </row>
@@ -25290,10 +25312,10 @@
         <v>49</v>
       </c>
       <c r="B1242" t="s" s="2">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="C1242" t="s" s="2">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="D1242" s="2"/>
     </row>
@@ -25302,10 +25324,10 @@
         <v>49</v>
       </c>
       <c r="B1243" t="s" s="2">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="C1243" t="s" s="2">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="D1243" s="2"/>
     </row>
@@ -25314,13 +25336,13 @@
         <v>49</v>
       </c>
       <c r="B1244" t="s" s="2">
+        <v>2678</v>
+      </c>
+      <c r="C1244" t="s" s="2">
+        <v>2679</v>
+      </c>
+      <c r="D1244" t="s" s="2">
         <v>2680</v>
-      </c>
-      <c r="C1244" t="s" s="2">
-        <v>2681</v>
-      </c>
-      <c r="D1244" t="s" s="2">
-        <v>2682</v>
       </c>
     </row>
     <row r="1245">
@@ -25328,13 +25350,13 @@
         <v>49</v>
       </c>
       <c r="B1245" t="s" s="2">
+        <v>2681</v>
+      </c>
+      <c r="C1245" t="s" s="2">
+        <v>2682</v>
+      </c>
+      <c r="D1245" t="s" s="2">
         <v>2683</v>
-      </c>
-      <c r="C1245" t="s" s="2">
-        <v>2684</v>
-      </c>
-      <c r="D1245" t="s" s="2">
-        <v>2685</v>
       </c>
     </row>
     <row r="1246">
@@ -25342,10 +25364,10 @@
         <v>49</v>
       </c>
       <c r="B1246" t="s" s="2">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="C1246" t="s" s="2">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="D1246" s="2"/>
     </row>
@@ -25354,13 +25376,13 @@
         <v>49</v>
       </c>
       <c r="B1247" t="s" s="2">
+        <v>2686</v>
+      </c>
+      <c r="C1247" t="s" s="2">
+        <v>2687</v>
+      </c>
+      <c r="D1247" t="s" s="2">
         <v>2688</v>
-      </c>
-      <c r="C1247" t="s" s="2">
-        <v>2689</v>
-      </c>
-      <c r="D1247" t="s" s="2">
-        <v>2690</v>
       </c>
     </row>
     <row r="1248">
@@ -25368,13 +25390,13 @@
         <v>49</v>
       </c>
       <c r="B1248" t="s" s="2">
+        <v>2689</v>
+      </c>
+      <c r="C1248" t="s" s="2">
+        <v>2690</v>
+      </c>
+      <c r="D1248" t="s" s="2">
         <v>2691</v>
-      </c>
-      <c r="C1248" t="s" s="2">
-        <v>2692</v>
-      </c>
-      <c r="D1248" t="s" s="2">
-        <v>2693</v>
       </c>
     </row>
     <row r="1249">
@@ -25382,13 +25404,13 @@
         <v>49</v>
       </c>
       <c r="B1249" t="s" s="2">
+        <v>2692</v>
+      </c>
+      <c r="C1249" t="s" s="2">
+        <v>2693</v>
+      </c>
+      <c r="D1249" t="s" s="2">
         <v>2694</v>
-      </c>
-      <c r="C1249" t="s" s="2">
-        <v>2695</v>
-      </c>
-      <c r="D1249" t="s" s="2">
-        <v>2696</v>
       </c>
     </row>
     <row r="1250">
@@ -25396,10 +25418,10 @@
         <v>49</v>
       </c>
       <c r="B1250" t="s" s="2">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="C1250" t="s" s="2">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="D1250" s="2"/>
     </row>
@@ -25408,10 +25430,10 @@
         <v>49</v>
       </c>
       <c r="B1251" t="s" s="2">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="C1251" t="s" s="2">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="D1251" s="2"/>
     </row>
@@ -25420,10 +25442,10 @@
         <v>49</v>
       </c>
       <c r="B1252" t="s" s="2">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="C1252" t="s" s="2">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="D1252" s="2"/>
     </row>
@@ -25432,10 +25454,10 @@
         <v>49</v>
       </c>
       <c r="B1253" t="s" s="2">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="C1253" t="s" s="2">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="D1253" s="2"/>
     </row>
@@ -25444,10 +25466,10 @@
         <v>49</v>
       </c>
       <c r="B1254" t="s" s="2">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="C1254" t="s" s="2">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="D1254" s="2"/>
     </row>
@@ -25456,10 +25478,10 @@
         <v>49</v>
       </c>
       <c r="B1255" t="s" s="2">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="C1255" t="s" s="2">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="D1255" s="2"/>
     </row>
@@ -25468,10 +25490,10 @@
         <v>49</v>
       </c>
       <c r="B1256" t="s" s="2">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="C1256" t="s" s="2">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="D1256" s="2"/>
     </row>
@@ -25480,10 +25502,10 @@
         <v>49</v>
       </c>
       <c r="B1257" t="s" s="2">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="C1257" t="s" s="2">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="D1257" s="2"/>
     </row>
@@ -25492,10 +25514,10 @@
         <v>49</v>
       </c>
       <c r="B1258" t="s" s="2">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="C1258" t="s" s="2">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="D1258" s="2"/>
     </row>
@@ -25504,10 +25526,10 @@
         <v>49</v>
       </c>
       <c r="B1259" t="s" s="2">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="C1259" t="s" s="2">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="D1259" s="2"/>
     </row>
@@ -25516,10 +25538,10 @@
         <v>49</v>
       </c>
       <c r="B1260" t="s" s="2">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="C1260" t="s" s="2">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="D1260" s="2"/>
     </row>
@@ -25528,10 +25550,10 @@
         <v>49</v>
       </c>
       <c r="B1261" t="s" s="2">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="C1261" t="s" s="2">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="D1261" s="2"/>
     </row>
@@ -25540,10 +25562,10 @@
         <v>49</v>
       </c>
       <c r="B1262" t="s" s="2">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="C1262" t="s" s="2">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="D1262" s="2"/>
     </row>
@@ -25552,10 +25574,10 @@
         <v>49</v>
       </c>
       <c r="B1263" t="s" s="2">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="C1263" t="s" s="2">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="D1263" s="2"/>
     </row>
@@ -25564,10 +25586,10 @@
         <v>49</v>
       </c>
       <c r="B1264" t="s" s="2">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="C1264" t="s" s="2">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="D1264" s="2"/>
     </row>
@@ -25576,10 +25598,10 @@
         <v>49</v>
       </c>
       <c r="B1265" t="s" s="2">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="C1265" t="s" s="2">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D1265" s="2"/>
     </row>
@@ -25588,13 +25610,13 @@
         <v>49</v>
       </c>
       <c r="B1266" t="s" s="2">
+        <v>2727</v>
+      </c>
+      <c r="C1266" t="s" s="2">
+        <v>2728</v>
+      </c>
+      <c r="D1266" t="s" s="2">
         <v>2729</v>
-      </c>
-      <c r="C1266" t="s" s="2">
-        <v>2730</v>
-      </c>
-      <c r="D1266" t="s" s="2">
-        <v>2731</v>
       </c>
     </row>
     <row r="1267">
@@ -25602,13 +25624,13 @@
         <v>49</v>
       </c>
       <c r="B1267" t="s" s="2">
+        <v>2730</v>
+      </c>
+      <c r="C1267" t="s" s="2">
+        <v>2731</v>
+      </c>
+      <c r="D1267" t="s" s="2">
         <v>2732</v>
-      </c>
-      <c r="C1267" t="s" s="2">
-        <v>2733</v>
-      </c>
-      <c r="D1267" t="s" s="2">
-        <v>2734</v>
       </c>
     </row>
     <row r="1268">
@@ -25616,13 +25638,13 @@
         <v>49</v>
       </c>
       <c r="B1268" t="s" s="2">
+        <v>2733</v>
+      </c>
+      <c r="C1268" t="s" s="2">
+        <v>2734</v>
+      </c>
+      <c r="D1268" t="s" s="2">
         <v>2735</v>
-      </c>
-      <c r="C1268" t="s" s="2">
-        <v>2736</v>
-      </c>
-      <c r="D1268" t="s" s="2">
-        <v>2737</v>
       </c>
     </row>
     <row r="1269">
@@ -25630,13 +25652,13 @@
         <v>49</v>
       </c>
       <c r="B1269" t="s" s="2">
+        <v>2736</v>
+      </c>
+      <c r="C1269" t="s" s="2">
+        <v>2737</v>
+      </c>
+      <c r="D1269" t="s" s="2">
         <v>2738</v>
-      </c>
-      <c r="C1269" t="s" s="2">
-        <v>2739</v>
-      </c>
-      <c r="D1269" t="s" s="2">
-        <v>2740</v>
       </c>
     </row>
     <row r="1270">
@@ -25644,13 +25666,13 @@
         <v>49</v>
       </c>
       <c r="B1270" t="s" s="2">
+        <v>2739</v>
+      </c>
+      <c r="C1270" t="s" s="2">
+        <v>2740</v>
+      </c>
+      <c r="D1270" t="s" s="2">
         <v>2741</v>
-      </c>
-      <c r="C1270" t="s" s="2">
-        <v>2742</v>
-      </c>
-      <c r="D1270" t="s" s="2">
-        <v>2743</v>
       </c>
     </row>
     <row r="1271">
@@ -25658,10 +25680,10 @@
         <v>49</v>
       </c>
       <c r="B1271" t="s" s="2">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="C1271" t="s" s="2">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="D1271" s="2"/>
     </row>
@@ -25670,10 +25692,10 @@
         <v>49</v>
       </c>
       <c r="B1272" t="s" s="2">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="C1272" t="s" s="2">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="D1272" s="2"/>
     </row>
@@ -25682,10 +25704,10 @@
         <v>49</v>
       </c>
       <c r="B1273" t="s" s="2">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="C1273" t="s" s="2">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="D1273" s="2"/>
     </row>
@@ -25694,10 +25716,10 @@
         <v>49</v>
       </c>
       <c r="B1274" t="s" s="2">
-        <v>2750</v>
+        <v>2748</v>
       </c>
       <c r="C1274" t="s" s="2">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="D1274" s="2"/>
     </row>
@@ -25706,10 +25728,10 @@
         <v>49</v>
       </c>
       <c r="B1275" t="s" s="2">
-        <v>2752</v>
+        <v>2750</v>
       </c>
       <c r="C1275" t="s" s="2">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="D1275" s="2"/>
     </row>
@@ -25718,13 +25740,13 @@
         <v>49</v>
       </c>
       <c r="B1276" t="s" s="2">
+        <v>2752</v>
+      </c>
+      <c r="C1276" t="s" s="2">
+        <v>2753</v>
+      </c>
+      <c r="D1276" t="s" s="2">
         <v>2754</v>
-      </c>
-      <c r="C1276" t="s" s="2">
-        <v>2755</v>
-      </c>
-      <c r="D1276" t="s" s="2">
-        <v>2756</v>
       </c>
     </row>
     <row r="1277">
@@ -25732,10 +25754,10 @@
         <v>49</v>
       </c>
       <c r="B1277" t="s" s="2">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="C1277" t="s" s="2">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="D1277" s="2"/>
     </row>
@@ -25744,10 +25766,10 @@
         <v>49</v>
       </c>
       <c r="B1278" t="s" s="2">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="C1278" t="s" s="2">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="D1278" s="2"/>
     </row>
@@ -25756,10 +25778,10 @@
         <v>49</v>
       </c>
       <c r="B1279" t="s" s="2">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="C1279" t="s" s="2">
-        <v>2762</v>
+        <v>2760</v>
       </c>
       <c r="D1279" s="2"/>
     </row>
@@ -25768,10 +25790,10 @@
         <v>49</v>
       </c>
       <c r="B1280" t="s" s="2">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="C1280" t="s" s="2">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="D1280" s="2"/>
     </row>
@@ -25780,13 +25802,13 @@
         <v>49</v>
       </c>
       <c r="B1281" t="s" s="2">
+        <v>2763</v>
+      </c>
+      <c r="C1281" t="s" s="2">
+        <v>2764</v>
+      </c>
+      <c r="D1281" t="s" s="2">
         <v>2765</v>
-      </c>
-      <c r="C1281" t="s" s="2">
-        <v>2766</v>
-      </c>
-      <c r="D1281" t="s" s="2">
-        <v>2767</v>
       </c>
     </row>
     <row r="1282">
@@ -25794,13 +25816,13 @@
         <v>49</v>
       </c>
       <c r="B1282" t="s" s="2">
+        <v>2766</v>
+      </c>
+      <c r="C1282" t="s" s="2">
+        <v>2767</v>
+      </c>
+      <c r="D1282" t="s" s="2">
         <v>2768</v>
-      </c>
-      <c r="C1282" t="s" s="2">
-        <v>2769</v>
-      </c>
-      <c r="D1282" t="s" s="2">
-        <v>2770</v>
       </c>
     </row>
     <row r="1283">
@@ -25808,13 +25830,13 @@
         <v>49</v>
       </c>
       <c r="B1283" t="s" s="2">
+        <v>2769</v>
+      </c>
+      <c r="C1283" t="s" s="2">
+        <v>2770</v>
+      </c>
+      <c r="D1283" t="s" s="2">
         <v>2771</v>
-      </c>
-      <c r="C1283" t="s" s="2">
-        <v>2772</v>
-      </c>
-      <c r="D1283" t="s" s="2">
-        <v>2773</v>
       </c>
     </row>
     <row r="1284">
@@ -25822,13 +25844,13 @@
         <v>49</v>
       </c>
       <c r="B1284" t="s" s="2">
+        <v>2772</v>
+      </c>
+      <c r="C1284" t="s" s="2">
+        <v>2773</v>
+      </c>
+      <c r="D1284" t="s" s="2">
         <v>2774</v>
-      </c>
-      <c r="C1284" t="s" s="2">
-        <v>2775</v>
-      </c>
-      <c r="D1284" t="s" s="2">
-        <v>2776</v>
       </c>
     </row>
     <row r="1285">
@@ -25836,13 +25858,13 @@
         <v>49</v>
       </c>
       <c r="B1285" t="s" s="2">
+        <v>2775</v>
+      </c>
+      <c r="C1285" t="s" s="2">
+        <v>2776</v>
+      </c>
+      <c r="D1285" t="s" s="2">
         <v>2777</v>
-      </c>
-      <c r="C1285" t="s" s="2">
-        <v>2778</v>
-      </c>
-      <c r="D1285" t="s" s="2">
-        <v>2779</v>
       </c>
     </row>
     <row r="1286">
@@ -25850,13 +25872,13 @@
         <v>49</v>
       </c>
       <c r="B1286" t="s" s="2">
+        <v>2778</v>
+      </c>
+      <c r="C1286" t="s" s="2">
+        <v>2779</v>
+      </c>
+      <c r="D1286" t="s" s="2">
         <v>2780</v>
-      </c>
-      <c r="C1286" t="s" s="2">
-        <v>2781</v>
-      </c>
-      <c r="D1286" t="s" s="2">
-        <v>2782</v>
       </c>
     </row>
     <row r="1287">
@@ -25864,13 +25886,13 @@
         <v>49</v>
       </c>
       <c r="B1287" t="s" s="2">
+        <v>2781</v>
+      </c>
+      <c r="C1287" t="s" s="2">
+        <v>2782</v>
+      </c>
+      <c r="D1287" t="s" s="2">
         <v>2783</v>
-      </c>
-      <c r="C1287" t="s" s="2">
-        <v>2784</v>
-      </c>
-      <c r="D1287" t="s" s="2">
-        <v>2785</v>
       </c>
     </row>
     <row r="1288">
@@ -25878,13 +25900,13 @@
         <v>49</v>
       </c>
       <c r="B1288" t="s" s="2">
+        <v>2784</v>
+      </c>
+      <c r="C1288" t="s" s="2">
+        <v>2785</v>
+      </c>
+      <c r="D1288" t="s" s="2">
         <v>2786</v>
-      </c>
-      <c r="C1288" t="s" s="2">
-        <v>2787</v>
-      </c>
-      <c r="D1288" t="s" s="2">
-        <v>2788</v>
       </c>
     </row>
     <row r="1289">
@@ -25892,13 +25914,13 @@
         <v>49</v>
       </c>
       <c r="B1289" t="s" s="2">
+        <v>2787</v>
+      </c>
+      <c r="C1289" t="s" s="2">
+        <v>2788</v>
+      </c>
+      <c r="D1289" t="s" s="2">
         <v>2789</v>
-      </c>
-      <c r="C1289" t="s" s="2">
-        <v>2790</v>
-      </c>
-      <c r="D1289" t="s" s="2">
-        <v>2791</v>
       </c>
     </row>
     <row r="1290">
@@ -25906,13 +25928,13 @@
         <v>49</v>
       </c>
       <c r="B1290" t="s" s="2">
+        <v>2790</v>
+      </c>
+      <c r="C1290" t="s" s="2">
+        <v>2791</v>
+      </c>
+      <c r="D1290" t="s" s="2">
         <v>2792</v>
-      </c>
-      <c r="C1290" t="s" s="2">
-        <v>2793</v>
-      </c>
-      <c r="D1290" t="s" s="2">
-        <v>2794</v>
       </c>
     </row>
     <row r="1291">
@@ -25920,13 +25942,13 @@
         <v>49</v>
       </c>
       <c r="B1291" t="s" s="2">
+        <v>2793</v>
+      </c>
+      <c r="C1291" t="s" s="2">
+        <v>2794</v>
+      </c>
+      <c r="D1291" t="s" s="2">
         <v>2795</v>
-      </c>
-      <c r="C1291" t="s" s="2">
-        <v>2796</v>
-      </c>
-      <c r="D1291" t="s" s="2">
-        <v>2797</v>
       </c>
     </row>
     <row r="1292">
@@ -25934,13 +25956,13 @@
         <v>49</v>
       </c>
       <c r="B1292" t="s" s="2">
+        <v>2796</v>
+      </c>
+      <c r="C1292" t="s" s="2">
+        <v>2797</v>
+      </c>
+      <c r="D1292" t="s" s="2">
         <v>2798</v>
-      </c>
-      <c r="C1292" t="s" s="2">
-        <v>2799</v>
-      </c>
-      <c r="D1292" t="s" s="2">
-        <v>2800</v>
       </c>
     </row>
     <row r="1293">
@@ -25948,13 +25970,13 @@
         <v>49</v>
       </c>
       <c r="B1293" t="s" s="2">
+        <v>2799</v>
+      </c>
+      <c r="C1293" t="s" s="2">
+        <v>2800</v>
+      </c>
+      <c r="D1293" t="s" s="2">
         <v>2801</v>
-      </c>
-      <c r="C1293" t="s" s="2">
-        <v>2802</v>
-      </c>
-      <c r="D1293" t="s" s="2">
-        <v>2803</v>
       </c>
     </row>
     <row r="1294">
@@ -25962,13 +25984,13 @@
         <v>49</v>
       </c>
       <c r="B1294" t="s" s="2">
+        <v>2802</v>
+      </c>
+      <c r="C1294" t="s" s="2">
+        <v>2803</v>
+      </c>
+      <c r="D1294" t="s" s="2">
         <v>2804</v>
-      </c>
-      <c r="C1294" t="s" s="2">
-        <v>2805</v>
-      </c>
-      <c r="D1294" t="s" s="2">
-        <v>2806</v>
       </c>
     </row>
     <row r="1295">
@@ -25976,13 +25998,13 @@
         <v>49</v>
       </c>
       <c r="B1295" t="s" s="2">
+        <v>2805</v>
+      </c>
+      <c r="C1295" t="s" s="2">
+        <v>2806</v>
+      </c>
+      <c r="D1295" t="s" s="2">
         <v>2807</v>
-      </c>
-      <c r="C1295" t="s" s="2">
-        <v>2808</v>
-      </c>
-      <c r="D1295" t="s" s="2">
-        <v>2809</v>
       </c>
     </row>
     <row r="1296">
@@ -25990,13 +26012,13 @@
         <v>49</v>
       </c>
       <c r="B1296" t="s" s="2">
+        <v>2808</v>
+      </c>
+      <c r="C1296" t="s" s="2">
+        <v>2809</v>
+      </c>
+      <c r="D1296" t="s" s="2">
         <v>2810</v>
-      </c>
-      <c r="C1296" t="s" s="2">
-        <v>2811</v>
-      </c>
-      <c r="D1296" t="s" s="2">
-        <v>2812</v>
       </c>
     </row>
     <row r="1297">
@@ -26004,13 +26026,13 @@
         <v>49</v>
       </c>
       <c r="B1297" t="s" s="2">
+        <v>2811</v>
+      </c>
+      <c r="C1297" t="s" s="2">
+        <v>2812</v>
+      </c>
+      <c r="D1297" t="s" s="2">
         <v>2813</v>
-      </c>
-      <c r="C1297" t="s" s="2">
-        <v>2814</v>
-      </c>
-      <c r="D1297" t="s" s="2">
-        <v>2815</v>
       </c>
     </row>
     <row r="1298">
@@ -26018,13 +26040,13 @@
         <v>49</v>
       </c>
       <c r="B1298" t="s" s="2">
+        <v>2814</v>
+      </c>
+      <c r="C1298" t="s" s="2">
+        <v>2815</v>
+      </c>
+      <c r="D1298" t="s" s="2">
         <v>2816</v>
-      </c>
-      <c r="C1298" t="s" s="2">
-        <v>2817</v>
-      </c>
-      <c r="D1298" t="s" s="2">
-        <v>2818</v>
       </c>
     </row>
     <row r="1299">
@@ -26032,13 +26054,13 @@
         <v>49</v>
       </c>
       <c r="B1299" t="s" s="2">
+        <v>2817</v>
+      </c>
+      <c r="C1299" t="s" s="2">
+        <v>2818</v>
+      </c>
+      <c r="D1299" t="s" s="2">
         <v>2819</v>
-      </c>
-      <c r="C1299" t="s" s="2">
-        <v>2820</v>
-      </c>
-      <c r="D1299" t="s" s="2">
-        <v>2821</v>
       </c>
     </row>
     <row r="1300">
@@ -26046,13 +26068,13 @@
         <v>49</v>
       </c>
       <c r="B1300" t="s" s="2">
+        <v>2820</v>
+      </c>
+      <c r="C1300" t="s" s="2">
+        <v>2821</v>
+      </c>
+      <c r="D1300" t="s" s="2">
         <v>2822</v>
-      </c>
-      <c r="C1300" t="s" s="2">
-        <v>2823</v>
-      </c>
-      <c r="D1300" t="s" s="2">
-        <v>2824</v>
       </c>
     </row>
     <row r="1301">
@@ -26060,10 +26082,10 @@
         <v>49</v>
       </c>
       <c r="B1301" t="s" s="2">
-        <v>2825</v>
+        <v>2823</v>
       </c>
       <c r="C1301" t="s" s="2">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="D1301" s="2"/>
     </row>
@@ -26072,13 +26094,13 @@
         <v>49</v>
       </c>
       <c r="B1302" t="s" s="2">
+        <v>2824</v>
+      </c>
+      <c r="C1302" t="s" s="2">
+        <v>2825</v>
+      </c>
+      <c r="D1302" t="s" s="2">
         <v>2826</v>
-      </c>
-      <c r="C1302" t="s" s="2">
-        <v>2827</v>
-      </c>
-      <c r="D1302" t="s" s="2">
-        <v>2828</v>
       </c>
     </row>
     <row r="1303">
@@ -26086,13 +26108,13 @@
         <v>49</v>
       </c>
       <c r="B1303" t="s" s="2">
+        <v>2827</v>
+      </c>
+      <c r="C1303" t="s" s="2">
+        <v>2828</v>
+      </c>
+      <c r="D1303" t="s" s="2">
         <v>2829</v>
-      </c>
-      <c r="C1303" t="s" s="2">
-        <v>2830</v>
-      </c>
-      <c r="D1303" t="s" s="2">
-        <v>2831</v>
       </c>
     </row>
     <row r="1304">
@@ -26100,13 +26122,13 @@
         <v>49</v>
       </c>
       <c r="B1304" t="s" s="2">
+        <v>2830</v>
+      </c>
+      <c r="C1304" t="s" s="2">
+        <v>2831</v>
+      </c>
+      <c r="D1304" t="s" s="2">
         <v>2832</v>
-      </c>
-      <c r="C1304" t="s" s="2">
-        <v>2833</v>
-      </c>
-      <c r="D1304" t="s" s="2">
-        <v>2834</v>
       </c>
     </row>
     <row r="1305">
@@ -26114,10 +26136,10 @@
         <v>49</v>
       </c>
       <c r="B1305" t="s" s="2">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="C1305" t="s" s="2">
-        <v>2836</v>
+        <v>2834</v>
       </c>
       <c r="D1305" s="2"/>
     </row>
@@ -26126,10 +26148,10 @@
         <v>49</v>
       </c>
       <c r="B1306" t="s" s="2">
-        <v>2837</v>
+        <v>2835</v>
       </c>
       <c r="C1306" t="s" s="2">
-        <v>2838</v>
+        <v>2836</v>
       </c>
       <c r="D1306" s="2"/>
     </row>
@@ -26138,10 +26160,10 @@
         <v>49</v>
       </c>
       <c r="B1307" t="s" s="2">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="C1307" t="s" s="2">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="D1307" s="2"/>
     </row>
@@ -26150,10 +26172,10 @@
         <v>49</v>
       </c>
       <c r="B1308" t="s" s="2">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="C1308" t="s" s="2">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="D1308" s="2"/>
     </row>
@@ -26162,10 +26184,10 @@
         <v>49</v>
       </c>
       <c r="B1309" t="s" s="2">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="C1309" t="s" s="2">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="D1309" s="2"/>
     </row>
@@ -26174,10 +26196,10 @@
         <v>49</v>
       </c>
       <c r="B1310" t="s" s="2">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="C1310" t="s" s="2">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="D1310" s="2"/>
     </row>
@@ -26186,13 +26208,13 @@
         <v>49</v>
       </c>
       <c r="B1311" t="s" s="2">
+        <v>2845</v>
+      </c>
+      <c r="C1311" t="s" s="2">
+        <v>2846</v>
+      </c>
+      <c r="D1311" t="s" s="2">
         <v>2847</v>
-      </c>
-      <c r="C1311" t="s" s="2">
-        <v>2848</v>
-      </c>
-      <c r="D1311" t="s" s="2">
-        <v>2849</v>
       </c>
     </row>
     <row r="1312">
@@ -26200,10 +26222,10 @@
         <v>49</v>
       </c>
       <c r="B1312" t="s" s="2">
-        <v>2850</v>
+        <v>2848</v>
       </c>
       <c r="C1312" t="s" s="2">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="D1312" s="2"/>
     </row>
@@ -26212,10 +26234,10 @@
         <v>49</v>
       </c>
       <c r="B1313" t="s" s="2">
-        <v>2852</v>
+        <v>2850</v>
       </c>
       <c r="C1313" t="s" s="2">
-        <v>2853</v>
+        <v>2851</v>
       </c>
       <c r="D1313" s="2"/>
     </row>
@@ -26224,10 +26246,10 @@
         <v>49</v>
       </c>
       <c r="B1314" t="s" s="2">
-        <v>2854</v>
+        <v>2852</v>
       </c>
       <c r="C1314" t="s" s="2">
-        <v>2855</v>
+        <v>2853</v>
       </c>
       <c r="D1314" s="2"/>
     </row>
@@ -26236,10 +26258,10 @@
         <v>49</v>
       </c>
       <c r="B1315" t="s" s="2">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="C1315" t="s" s="2">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="D1315" s="2"/>
     </row>
@@ -26248,10 +26270,10 @@
         <v>49</v>
       </c>
       <c r="B1316" t="s" s="2">
-        <v>2858</v>
+        <v>2856</v>
       </c>
       <c r="C1316" t="s" s="2">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="D1316" s="2"/>
     </row>
@@ -26260,10 +26282,10 @@
         <v>49</v>
       </c>
       <c r="B1317" t="s" s="2">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="C1317" t="s" s="2">
-        <v>2861</v>
+        <v>2859</v>
       </c>
       <c r="D1317" s="2"/>
     </row>
@@ -26272,13 +26294,13 @@
         <v>49</v>
       </c>
       <c r="B1318" t="s" s="2">
+        <v>2860</v>
+      </c>
+      <c r="C1318" t="s" s="2">
+        <v>2861</v>
+      </c>
+      <c r="D1318" t="s" s="2">
         <v>2862</v>
-      </c>
-      <c r="C1318" t="s" s="2">
-        <v>2863</v>
-      </c>
-      <c r="D1318" t="s" s="2">
-        <v>2864</v>
       </c>
     </row>
     <row r="1319">
@@ -26286,7 +26308,7 @@
         <v>49</v>
       </c>
       <c r="B1319" t="s" s="2">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="C1319" t="s" s="2">
         <v>778</v>
@@ -26298,10 +26320,10 @@
         <v>49</v>
       </c>
       <c r="B1320" t="s" s="2">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="C1320" t="s" s="2">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="D1320" s="2"/>
     </row>
@@ -26310,10 +26332,10 @@
         <v>49</v>
       </c>
       <c r="B1321" t="s" s="2">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="C1321" t="s" s="2">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="D1321" s="2"/>
     </row>
@@ -26322,10 +26344,10 @@
         <v>49</v>
       </c>
       <c r="B1322" t="s" s="2">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="C1322" t="s" s="2">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="D1322" s="2"/>
     </row>
@@ -26334,10 +26356,10 @@
         <v>49</v>
       </c>
       <c r="B1323" t="s" s="2">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="C1323" t="s" s="2">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="D1323" s="2"/>
     </row>
@@ -26346,10 +26368,10 @@
         <v>49</v>
       </c>
       <c r="B1324" t="s" s="2">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="C1324" t="s" s="2">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="D1324" s="2"/>
     </row>
@@ -26358,10 +26380,10 @@
         <v>49</v>
       </c>
       <c r="B1325" t="s" s="2">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="C1325" t="s" s="2">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="D1325" s="2"/>
     </row>
@@ -26370,7 +26392,7 @@
         <v>49</v>
       </c>
       <c r="B1326" t="s" s="2">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="C1326" t="s" s="2">
         <v>1902</v>
@@ -26382,7 +26404,7 @@
         <v>49</v>
       </c>
       <c r="B1327" t="s" s="2">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="C1327" t="s" s="2">
         <v>1904</v>
@@ -26394,10 +26416,10 @@
         <v>49</v>
       </c>
       <c r="B1328" t="s" s="2">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="C1328" t="s" s="2">
-        <v>2881</v>
+        <v>2879</v>
       </c>
       <c r="D1328" s="2"/>
     </row>
@@ -26406,10 +26428,10 @@
         <v>49</v>
       </c>
       <c r="B1329" t="s" s="2">
-        <v>2882</v>
+        <v>2880</v>
       </c>
       <c r="C1329" t="s" s="2">
-        <v>2883</v>
+        <v>2881</v>
       </c>
       <c r="D1329" s="2"/>
     </row>
@@ -26418,13 +26440,13 @@
         <v>49</v>
       </c>
       <c r="B1330" t="s" s="2">
+        <v>2882</v>
+      </c>
+      <c r="C1330" t="s" s="2">
+        <v>2883</v>
+      </c>
+      <c r="D1330" t="s" s="2">
         <v>2884</v>
-      </c>
-      <c r="C1330" t="s" s="2">
-        <v>2885</v>
-      </c>
-      <c r="D1330" t="s" s="2">
-        <v>2886</v>
       </c>
     </row>
     <row r="1331">
@@ -26432,10 +26454,10 @@
         <v>49</v>
       </c>
       <c r="B1331" t="s" s="2">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="C1331" t="s" s="2">
-        <v>2888</v>
+        <v>2886</v>
       </c>
       <c r="D1331" s="2"/>
     </row>
@@ -26444,10 +26466,10 @@
         <v>49</v>
       </c>
       <c r="B1332" t="s" s="2">
-        <v>2889</v>
+        <v>2887</v>
       </c>
       <c r="C1332" t="s" s="2">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="D1332" s="2"/>
     </row>
@@ -26456,10 +26478,10 @@
         <v>49</v>
       </c>
       <c r="B1333" t="s" s="2">
-        <v>2891</v>
+        <v>2889</v>
       </c>
       <c r="C1333" t="s" s="2">
-        <v>2892</v>
+        <v>2890</v>
       </c>
       <c r="D1333" s="2"/>
     </row>
@@ -26468,10 +26490,10 @@
         <v>49</v>
       </c>
       <c r="B1334" t="s" s="2">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="C1334" t="s" s="2">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="D1334" s="2"/>
     </row>
@@ -26480,10 +26502,10 @@
         <v>49</v>
       </c>
       <c r="B1335" t="s" s="2">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="C1335" t="s" s="2">
-        <v>2896</v>
+        <v>2894</v>
       </c>
       <c r="D1335" s="2"/>
     </row>
@@ -26492,10 +26514,10 @@
         <v>49</v>
       </c>
       <c r="B1336" t="s" s="2">
-        <v>2897</v>
+        <v>2895</v>
       </c>
       <c r="C1336" t="s" s="2">
-        <v>2830</v>
+        <v>2828</v>
       </c>
       <c r="D1336" s="2"/>
     </row>
@@ -26504,10 +26526,10 @@
         <v>49</v>
       </c>
       <c r="B1337" t="s" s="2">
-        <v>2898</v>
+        <v>2896</v>
       </c>
       <c r="C1337" t="s" s="2">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="D1337" s="2"/>
     </row>
@@ -26516,10 +26538,10 @@
         <v>49</v>
       </c>
       <c r="B1338" t="s" s="2">
-        <v>2900</v>
+        <v>2898</v>
       </c>
       <c r="C1338" t="s" s="2">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="D1338" s="2"/>
     </row>
@@ -26528,10 +26550,10 @@
         <v>49</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2902</v>
+        <v>2900</v>
       </c>
       <c r="C1339" t="s" s="2">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="D1339" s="2"/>
     </row>
@@ -26540,7 +26562,7 @@
         <v>49</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="C1340" t="s" s="2">
         <v>1718</v>
@@ -26552,10 +26574,10 @@
         <v>49</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26564,10 +26586,10 @@
         <v>49</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -26576,10 +26598,10 @@
         <v>49</v>
       </c>
       <c r="B1343" t="s" s="2">
-        <v>2909</v>
+        <v>2907</v>
       </c>
       <c r="C1343" t="s" s="2">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="D1343" s="2"/>
     </row>
@@ -26588,10 +26610,10 @@
         <v>49</v>
       </c>
       <c r="B1344" t="s" s="2">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="C1344" t="s" s="2">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="D1344" s="2"/>
     </row>
@@ -26600,10 +26622,10 @@
         <v>49</v>
       </c>
       <c r="B1345" t="s" s="2">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="C1345" t="s" s="2">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="D1345" s="2"/>
     </row>
@@ -26612,10 +26634,10 @@
         <v>49</v>
       </c>
       <c r="B1346" t="s" s="2">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="C1346" t="s" s="2">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="D1346" s="2"/>
     </row>
@@ -26624,10 +26646,10 @@
         <v>49</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="C1347" t="s" s="2">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="D1347" s="2"/>
     </row>
@@ -26636,10 +26658,10 @@
         <v>49</v>
       </c>
       <c r="B1348" t="s" s="2">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="C1348" t="s" s="2">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="D1348" s="2"/>
     </row>
@@ -26648,10 +26670,10 @@
         <v>49</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="C1349" t="s" s="2">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="D1349" s="2"/>
     </row>
@@ -26660,10 +26682,10 @@
         <v>49</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="C1350" t="s" s="2">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="D1350" s="2"/>
     </row>
@@ -26672,10 +26694,10 @@
         <v>49</v>
       </c>
       <c r="B1351" t="s" s="2">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="C1351" t="s" s="2">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="D1351" s="2"/>
     </row>
@@ -26684,10 +26706,10 @@
         <v>49</v>
       </c>
       <c r="B1352" t="s" s="2">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="C1352" t="s" s="2">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="D1352" s="2"/>
     </row>
@@ -26696,10 +26718,10 @@
         <v>49</v>
       </c>
       <c r="B1353" t="s" s="2">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="C1353" t="s" s="2">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="D1353" s="2"/>
     </row>
@@ -26708,10 +26730,10 @@
         <v>49</v>
       </c>
       <c r="B1354" t="s" s="2">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="C1354" t="s" s="2">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="D1354" s="2"/>
     </row>
@@ -26720,13 +26742,13 @@
         <v>49</v>
       </c>
       <c r="B1355" t="s" s="2">
+        <v>2931</v>
+      </c>
+      <c r="C1355" t="s" s="2">
+        <v>2932</v>
+      </c>
+      <c r="D1355" t="s" s="2">
         <v>2933</v>
-      </c>
-      <c r="C1355" t="s" s="2">
-        <v>2934</v>
-      </c>
-      <c r="D1355" t="s" s="2">
-        <v>2935</v>
       </c>
     </row>
     <row r="1356">
@@ -26734,13 +26756,13 @@
         <v>49</v>
       </c>
       <c r="B1356" t="s" s="2">
+        <v>2934</v>
+      </c>
+      <c r="C1356" t="s" s="2">
+        <v>2935</v>
+      </c>
+      <c r="D1356" t="s" s="2">
         <v>2936</v>
-      </c>
-      <c r="C1356" t="s" s="2">
-        <v>2937</v>
-      </c>
-      <c r="D1356" t="s" s="2">
-        <v>2938</v>
       </c>
     </row>
     <row r="1357">
@@ -26748,13 +26770,13 @@
         <v>49</v>
       </c>
       <c r="B1357" t="s" s="2">
+        <v>2937</v>
+      </c>
+      <c r="C1357" t="s" s="2">
+        <v>2938</v>
+      </c>
+      <c r="D1357" t="s" s="2">
         <v>2939</v>
-      </c>
-      <c r="C1357" t="s" s="2">
-        <v>2940</v>
-      </c>
-      <c r="D1357" t="s" s="2">
-        <v>2941</v>
       </c>
     </row>
     <row r="1358">
@@ -26762,13 +26784,13 @@
         <v>49</v>
       </c>
       <c r="B1358" t="s" s="2">
+        <v>2940</v>
+      </c>
+      <c r="C1358" t="s" s="2">
+        <v>2941</v>
+      </c>
+      <c r="D1358" t="s" s="2">
         <v>2942</v>
-      </c>
-      <c r="C1358" t="s" s="2">
-        <v>2943</v>
-      </c>
-      <c r="D1358" t="s" s="2">
-        <v>2944</v>
       </c>
     </row>
     <row r="1359">
@@ -26776,13 +26798,13 @@
         <v>49</v>
       </c>
       <c r="B1359" t="s" s="2">
+        <v>2943</v>
+      </c>
+      <c r="C1359" t="s" s="2">
+        <v>2944</v>
+      </c>
+      <c r="D1359" t="s" s="2">
         <v>2945</v>
-      </c>
-      <c r="C1359" t="s" s="2">
-        <v>2946</v>
-      </c>
-      <c r="D1359" t="s" s="2">
-        <v>2947</v>
       </c>
     </row>
     <row r="1360">
@@ -26790,10 +26812,10 @@
         <v>49</v>
       </c>
       <c r="B1360" t="s" s="2">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="C1360" t="s" s="2">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="D1360" s="2"/>
     </row>
@@ -26802,10 +26824,10 @@
         <v>49</v>
       </c>
       <c r="B1361" t="s" s="2">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="C1361" t="s" s="2">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="D1361" s="2"/>
     </row>
@@ -26814,10 +26836,10 @@
         <v>49</v>
       </c>
       <c r="B1362" t="s" s="2">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="C1362" t="s" s="2">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="D1362" s="2"/>
     </row>
@@ -26826,13 +26848,13 @@
         <v>49</v>
       </c>
       <c r="B1363" t="s" s="2">
+        <v>2952</v>
+      </c>
+      <c r="C1363" t="s" s="2">
+        <v>2953</v>
+      </c>
+      <c r="D1363" t="s" s="2">
         <v>2954</v>
-      </c>
-      <c r="C1363" t="s" s="2">
-        <v>2955</v>
-      </c>
-      <c r="D1363" t="s" s="2">
-        <v>2956</v>
       </c>
     </row>
     <row r="1364">
@@ -26840,10 +26862,10 @@
         <v>49</v>
       </c>
       <c r="B1364" t="s" s="2">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="C1364" t="s" s="2">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="D1364" s="2"/>
     </row>
@@ -26852,13 +26874,13 @@
         <v>49</v>
       </c>
       <c r="B1365" t="s" s="2">
+        <v>2957</v>
+      </c>
+      <c r="C1365" t="s" s="2">
+        <v>2958</v>
+      </c>
+      <c r="D1365" t="s" s="2">
         <v>2959</v>
-      </c>
-      <c r="C1365" t="s" s="2">
-        <v>2960</v>
-      </c>
-      <c r="D1365" t="s" s="2">
-        <v>2961</v>
       </c>
     </row>
     <row r="1366">
@@ -26866,10 +26888,10 @@
         <v>49</v>
       </c>
       <c r="B1366" t="s" s="2">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="C1366" t="s" s="2">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="D1366" s="2"/>
     </row>
@@ -26878,13 +26900,13 @@
         <v>49</v>
       </c>
       <c r="B1367" t="s" s="2">
+        <v>2962</v>
+      </c>
+      <c r="C1367" t="s" s="2">
+        <v>2963</v>
+      </c>
+      <c r="D1367" t="s" s="2">
         <v>2964</v>
-      </c>
-      <c r="C1367" t="s" s="2">
-        <v>2965</v>
-      </c>
-      <c r="D1367" t="s" s="2">
-        <v>2966</v>
       </c>
     </row>
     <row r="1368">
@@ -26892,10 +26914,10 @@
         <v>49</v>
       </c>
       <c r="B1368" t="s" s="2">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="C1368" t="s" s="2">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="D1368" s="2"/>
     </row>
@@ -26904,10 +26926,10 @@
         <v>49</v>
       </c>
       <c r="B1369" t="s" s="2">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="C1369" t="s" s="2">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="D1369" s="2"/>
     </row>
@@ -26916,13 +26938,13 @@
         <v>49</v>
       </c>
       <c r="B1370" t="s" s="2">
+        <v>2969</v>
+      </c>
+      <c r="C1370" t="s" s="2">
+        <v>2970</v>
+      </c>
+      <c r="D1370" t="s" s="2">
         <v>2971</v>
-      </c>
-      <c r="C1370" t="s" s="2">
-        <v>2972</v>
-      </c>
-      <c r="D1370" t="s" s="2">
-        <v>2973</v>
       </c>
     </row>
     <row r="1371">
@@ -26930,13 +26952,13 @@
         <v>49</v>
       </c>
       <c r="B1371" t="s" s="2">
+        <v>2972</v>
+      </c>
+      <c r="C1371" t="s" s="2">
+        <v>2973</v>
+      </c>
+      <c r="D1371" t="s" s="2">
         <v>2974</v>
-      </c>
-      <c r="C1371" t="s" s="2">
-        <v>2975</v>
-      </c>
-      <c r="D1371" t="s" s="2">
-        <v>2976</v>
       </c>
     </row>
     <row r="1372">
@@ -26944,13 +26966,13 @@
         <v>49</v>
       </c>
       <c r="B1372" t="s" s="2">
+        <v>2975</v>
+      </c>
+      <c r="C1372" t="s" s="2">
+        <v>2976</v>
+      </c>
+      <c r="D1372" t="s" s="2">
         <v>2977</v>
-      </c>
-      <c r="C1372" t="s" s="2">
-        <v>2978</v>
-      </c>
-      <c r="D1372" t="s" s="2">
-        <v>2979</v>
       </c>
     </row>
     <row r="1373">
@@ -26958,13 +26980,13 @@
         <v>49</v>
       </c>
       <c r="B1373" t="s" s="2">
+        <v>2978</v>
+      </c>
+      <c r="C1373" t="s" s="2">
+        <v>2979</v>
+      </c>
+      <c r="D1373" t="s" s="2">
         <v>2980</v>
-      </c>
-      <c r="C1373" t="s" s="2">
-        <v>2981</v>
-      </c>
-      <c r="D1373" t="s" s="2">
-        <v>2982</v>
       </c>
     </row>
     <row r="1374">
@@ -26972,13 +26994,13 @@
         <v>49</v>
       </c>
       <c r="B1374" t="s" s="2">
+        <v>2981</v>
+      </c>
+      <c r="C1374" t="s" s="2">
+        <v>2982</v>
+      </c>
+      <c r="D1374" t="s" s="2">
         <v>2983</v>
-      </c>
-      <c r="C1374" t="s" s="2">
-        <v>2984</v>
-      </c>
-      <c r="D1374" t="s" s="2">
-        <v>2985</v>
       </c>
     </row>
     <row r="1375">
@@ -26986,13 +27008,13 @@
         <v>49</v>
       </c>
       <c r="B1375" t="s" s="2">
+        <v>2984</v>
+      </c>
+      <c r="C1375" t="s" s="2">
+        <v>2985</v>
+      </c>
+      <c r="D1375" t="s" s="2">
         <v>2986</v>
-      </c>
-      <c r="C1375" t="s" s="2">
-        <v>2987</v>
-      </c>
-      <c r="D1375" t="s" s="2">
-        <v>2988</v>
       </c>
     </row>
     <row r="1376">
@@ -27000,13 +27022,13 @@
         <v>49</v>
       </c>
       <c r="B1376" t="s" s="2">
+        <v>2987</v>
+      </c>
+      <c r="C1376" t="s" s="2">
+        <v>2988</v>
+      </c>
+      <c r="D1376" t="s" s="2">
         <v>2989</v>
-      </c>
-      <c r="C1376" t="s" s="2">
-        <v>2990</v>
-      </c>
-      <c r="D1376" t="s" s="2">
-        <v>2991</v>
       </c>
     </row>
     <row r="1377">
@@ -27014,13 +27036,13 @@
         <v>49</v>
       </c>
       <c r="B1377" t="s" s="2">
+        <v>2990</v>
+      </c>
+      <c r="C1377" t="s" s="2">
+        <v>2991</v>
+      </c>
+      <c r="D1377" t="s" s="2">
         <v>2992</v>
-      </c>
-      <c r="C1377" t="s" s="2">
-        <v>2993</v>
-      </c>
-      <c r="D1377" t="s" s="2">
-        <v>2994</v>
       </c>
     </row>
     <row r="1378">
@@ -27028,13 +27050,13 @@
         <v>49</v>
       </c>
       <c r="B1378" t="s" s="2">
+        <v>2993</v>
+      </c>
+      <c r="C1378" t="s" s="2">
+        <v>2994</v>
+      </c>
+      <c r="D1378" t="s" s="2">
         <v>2995</v>
-      </c>
-      <c r="C1378" t="s" s="2">
-        <v>2996</v>
-      </c>
-      <c r="D1378" t="s" s="2">
-        <v>2997</v>
       </c>
     </row>
     <row r="1379">
@@ -27042,13 +27064,13 @@
         <v>49</v>
       </c>
       <c r="B1379" t="s" s="2">
+        <v>2996</v>
+      </c>
+      <c r="C1379" t="s" s="2">
+        <v>2997</v>
+      </c>
+      <c r="D1379" t="s" s="2">
         <v>2998</v>
-      </c>
-      <c r="C1379" t="s" s="2">
-        <v>2999</v>
-      </c>
-      <c r="D1379" t="s" s="2">
-        <v>3000</v>
       </c>
     </row>
     <row r="1380">
@@ -27056,10 +27078,10 @@
         <v>49</v>
       </c>
       <c r="B1380" t="s" s="2">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="C1380" t="s" s="2">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="D1380" s="2"/>
     </row>
@@ -27068,10 +27090,10 @@
         <v>49</v>
       </c>
       <c r="B1381" t="s" s="2">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C1381" t="s" s="2">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="D1381" s="2"/>
     </row>
@@ -27080,10 +27102,10 @@
         <v>49</v>
       </c>
       <c r="B1382" t="s" s="2">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="C1382" t="s" s="2">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="D1382" s="2"/>
     </row>
@@ -27092,10 +27114,10 @@
         <v>49</v>
       </c>
       <c r="B1383" t="s" s="2">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="C1383" t="s" s="2">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="D1383" s="2"/>
     </row>
@@ -27104,10 +27126,10 @@
         <v>49</v>
       </c>
       <c r="B1384" t="s" s="2">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="C1384" t="s" s="2">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="D1384" s="2"/>
     </row>
@@ -27116,10 +27138,10 @@
         <v>49</v>
       </c>
       <c r="B1385" t="s" s="2">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="C1385" t="s" s="2">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="D1385" s="2"/>
     </row>
@@ -27128,10 +27150,10 @@
         <v>49</v>
       </c>
       <c r="B1386" t="s" s="2">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="C1386" t="s" s="2">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="D1386" s="2"/>
     </row>
@@ -27140,10 +27162,10 @@
         <v>49</v>
       </c>
       <c r="B1387" t="s" s="2">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="C1387" t="s" s="2">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D1387" s="2"/>
     </row>
@@ -27152,13 +27174,13 @@
         <v>49</v>
       </c>
       <c r="B1388" t="s" s="2">
+        <v>3015</v>
+      </c>
+      <c r="C1388" t="s" s="2">
+        <v>3016</v>
+      </c>
+      <c r="D1388" t="s" s="2">
         <v>3017</v>
-      </c>
-      <c r="C1388" t="s" s="2">
-        <v>3018</v>
-      </c>
-      <c r="D1388" t="s" s="2">
-        <v>3019</v>
       </c>
     </row>
     <row r="1389">
@@ -27166,10 +27188,10 @@
         <v>49</v>
       </c>
       <c r="B1389" t="s" s="2">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="C1389" t="s" s="2">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="D1389" s="2"/>
     </row>
@@ -27178,13 +27200,13 @@
         <v>49</v>
       </c>
       <c r="B1390" t="s" s="2">
+        <v>3020</v>
+      </c>
+      <c r="C1390" t="s" s="2">
+        <v>3021</v>
+      </c>
+      <c r="D1390" t="s" s="2">
         <v>3022</v>
-      </c>
-      <c r="C1390" t="s" s="2">
-        <v>3023</v>
-      </c>
-      <c r="D1390" t="s" s="2">
-        <v>3024</v>
       </c>
     </row>
     <row r="1391">
@@ -27192,13 +27214,13 @@
         <v>49</v>
       </c>
       <c r="B1391" t="s" s="2">
+        <v>3023</v>
+      </c>
+      <c r="C1391" t="s" s="2">
+        <v>3024</v>
+      </c>
+      <c r="D1391" t="s" s="2">
         <v>3025</v>
-      </c>
-      <c r="C1391" t="s" s="2">
-        <v>3026</v>
-      </c>
-      <c r="D1391" t="s" s="2">
-        <v>3027</v>
       </c>
     </row>
     <row r="1392">
@@ -27206,13 +27228,13 @@
         <v>49</v>
       </c>
       <c r="B1392" t="s" s="2">
+        <v>3026</v>
+      </c>
+      <c r="C1392" t="s" s="2">
+        <v>3027</v>
+      </c>
+      <c r="D1392" t="s" s="2">
         <v>3028</v>
-      </c>
-      <c r="C1392" t="s" s="2">
-        <v>3029</v>
-      </c>
-      <c r="D1392" t="s" s="2">
-        <v>3030</v>
       </c>
     </row>
     <row r="1393">
@@ -27220,10 +27242,10 @@
         <v>49</v>
       </c>
       <c r="B1393" t="s" s="2">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="C1393" t="s" s="2">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="D1393" s="2"/>
     </row>
@@ -27232,13 +27254,13 @@
         <v>49</v>
       </c>
       <c r="B1394" t="s" s="2">
+        <v>3031</v>
+      </c>
+      <c r="C1394" t="s" s="2">
+        <v>3032</v>
+      </c>
+      <c r="D1394" t="s" s="2">
         <v>3033</v>
-      </c>
-      <c r="C1394" t="s" s="2">
-        <v>3034</v>
-      </c>
-      <c r="D1394" t="s" s="2">
-        <v>3035</v>
       </c>
     </row>
     <row r="1395">
@@ -27246,10 +27268,10 @@
         <v>49</v>
       </c>
       <c r="B1395" t="s" s="2">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="C1395" t="s" s="2">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="D1395" s="2"/>
     </row>
@@ -27258,13 +27280,13 @@
         <v>49</v>
       </c>
       <c r="B1396" t="s" s="2">
+        <v>3036</v>
+      </c>
+      <c r="C1396" t="s" s="2">
+        <v>3037</v>
+      </c>
+      <c r="D1396" t="s" s="2">
         <v>3038</v>
-      </c>
-      <c r="C1396" t="s" s="2">
-        <v>3039</v>
-      </c>
-      <c r="D1396" t="s" s="2">
-        <v>3040</v>
       </c>
     </row>
     <row r="1397">
@@ -27272,10 +27294,10 @@
         <v>49</v>
       </c>
       <c r="B1397" t="s" s="2">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="C1397" t="s" s="2">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="D1397" s="2"/>
     </row>
@@ -27284,10 +27306,10 @@
         <v>49</v>
       </c>
       <c r="B1398" t="s" s="2">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="C1398" t="s" s="2">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="D1398" s="2"/>
     </row>
@@ -27296,13 +27318,13 @@
         <v>49</v>
       </c>
       <c r="B1399" t="s" s="2">
+        <v>3043</v>
+      </c>
+      <c r="C1399" t="s" s="2">
+        <v>3044</v>
+      </c>
+      <c r="D1399" t="s" s="2">
         <v>3045</v>
-      </c>
-      <c r="C1399" t="s" s="2">
-        <v>3046</v>
-      </c>
-      <c r="D1399" t="s" s="2">
-        <v>3047</v>
       </c>
     </row>
     <row r="1400">
@@ -27310,10 +27332,10 @@
         <v>49</v>
       </c>
       <c r="B1400" t="s" s="2">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="C1400" t="s" s="2">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="D1400" s="2"/>
     </row>
@@ -27322,13 +27344,13 @@
         <v>49</v>
       </c>
       <c r="B1401" t="s" s="2">
+        <v>3048</v>
+      </c>
+      <c r="C1401" t="s" s="2">
+        <v>3049</v>
+      </c>
+      <c r="D1401" t="s" s="2">
         <v>3050</v>
-      </c>
-      <c r="C1401" t="s" s="2">
-        <v>3051</v>
-      </c>
-      <c r="D1401" t="s" s="2">
-        <v>3052</v>
       </c>
     </row>
     <row r="1402">
@@ -27336,13 +27358,13 @@
         <v>49</v>
       </c>
       <c r="B1402" t="s" s="2">
+        <v>3051</v>
+      </c>
+      <c r="C1402" t="s" s="2">
+        <v>3052</v>
+      </c>
+      <c r="D1402" t="s" s="2">
         <v>3053</v>
-      </c>
-      <c r="C1402" t="s" s="2">
-        <v>3054</v>
-      </c>
-      <c r="D1402" t="s" s="2">
-        <v>3055</v>
       </c>
     </row>
     <row r="1403">
@@ -27350,10 +27372,10 @@
         <v>49</v>
       </c>
       <c r="B1403" t="s" s="2">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="C1403" t="s" s="2">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="D1403" s="2"/>
     </row>
@@ -27362,10 +27384,10 @@
         <v>49</v>
       </c>
       <c r="B1404" t="s" s="2">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="C1404" t="s" s="2">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="D1404" s="2"/>
     </row>
@@ -27374,13 +27396,13 @@
         <v>49</v>
       </c>
       <c r="B1405" t="s" s="2">
+        <v>3058</v>
+      </c>
+      <c r="C1405" t="s" s="2">
+        <v>3059</v>
+      </c>
+      <c r="D1405" t="s" s="2">
         <v>3060</v>
-      </c>
-      <c r="C1405" t="s" s="2">
-        <v>3061</v>
-      </c>
-      <c r="D1405" t="s" s="2">
-        <v>3062</v>
       </c>
     </row>
     <row r="1406">
@@ -27388,10 +27410,10 @@
         <v>49</v>
       </c>
       <c r="B1406" t="s" s="2">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="C1406" t="s" s="2">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="D1406" s="2"/>
     </row>
@@ -27400,10 +27422,10 @@
         <v>49</v>
       </c>
       <c r="B1407" t="s" s="2">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="C1407" t="s" s="2">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="D1407" s="2"/>
     </row>
@@ -27412,10 +27434,10 @@
         <v>49</v>
       </c>
       <c r="B1408" t="s" s="2">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="C1408" t="s" s="2">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="D1408" s="2"/>
     </row>
@@ -27424,10 +27446,10 @@
         <v>49</v>
       </c>
       <c r="B1409" t="s" s="2">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="C1409" t="s" s="2">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="D1409" s="2"/>
     </row>
@@ -27436,13 +27458,13 @@
         <v>49</v>
       </c>
       <c r="B1410" t="s" s="2">
+        <v>3069</v>
+      </c>
+      <c r="C1410" t="s" s="2">
+        <v>3070</v>
+      </c>
+      <c r="D1410" t="s" s="2">
         <v>3071</v>
-      </c>
-      <c r="C1410" t="s" s="2">
-        <v>3072</v>
-      </c>
-      <c r="D1410" t="s" s="2">
-        <v>3073</v>
       </c>
     </row>
     <row r="1411">
@@ -27450,10 +27472,10 @@
         <v>49</v>
       </c>
       <c r="B1411" t="s" s="2">
-        <v>3074</v>
+        <v>3072</v>
       </c>
       <c r="C1411" t="s" s="2">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="D1411" s="2"/>
     </row>
@@ -27462,10 +27484,10 @@
         <v>49</v>
       </c>
       <c r="B1412" t="s" s="2">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="C1412" t="s" s="2">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="D1412" s="2"/>
     </row>
@@ -27474,10 +27496,10 @@
         <v>49</v>
       </c>
       <c r="B1413" t="s" s="2">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="C1413" t="s" s="2">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="D1413" s="2"/>
     </row>
@@ -27486,10 +27508,10 @@
         <v>49</v>
       </c>
       <c r="B1414" t="s" s="2">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="C1414" t="s" s="2">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="D1414" s="2"/>
     </row>
@@ -27498,10 +27520,10 @@
         <v>49</v>
       </c>
       <c r="B1415" t="s" s="2">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="C1415" t="s" s="2">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="D1415" s="2"/>
     </row>
@@ -27510,10 +27532,10 @@
         <v>49</v>
       </c>
       <c r="B1416" t="s" s="2">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="C1416" t="s" s="2">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="D1416" s="2"/>
     </row>
@@ -27522,10 +27544,10 @@
         <v>49</v>
       </c>
       <c r="B1417" t="s" s="2">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="C1417" t="s" s="2">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="D1417" s="2"/>
     </row>
@@ -27534,10 +27556,10 @@
         <v>49</v>
       </c>
       <c r="B1418" t="s" s="2">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="C1418" t="s" s="2">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="D1418" s="2"/>
     </row>
@@ -27546,10 +27568,10 @@
         <v>49</v>
       </c>
       <c r="B1419" t="s" s="2">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1419" t="s" s="2">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="D1419" s="2"/>
     </row>
@@ -27558,10 +27580,10 @@
         <v>49</v>
       </c>
       <c r="B1420" t="s" s="2">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="C1420" t="s" s="2">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="D1420" s="2"/>
     </row>
@@ -27570,10 +27592,10 @@
         <v>49</v>
       </c>
       <c r="B1421" t="s" s="2">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="C1421" t="s" s="2">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="D1421" s="2"/>
     </row>
@@ -27582,10 +27604,10 @@
         <v>49</v>
       </c>
       <c r="B1422" t="s" s="2">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="C1422" t="s" s="2">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="D1422" s="2"/>
     </row>
@@ -27594,13 +27616,13 @@
         <v>49</v>
       </c>
       <c r="B1423" t="s" s="2">
+        <v>3096</v>
+      </c>
+      <c r="C1423" t="s" s="2">
+        <v>3097</v>
+      </c>
+      <c r="D1423" t="s" s="2">
         <v>3098</v>
-      </c>
-      <c r="C1423" t="s" s="2">
-        <v>3099</v>
-      </c>
-      <c r="D1423" t="s" s="2">
-        <v>3100</v>
       </c>
     </row>
     <row r="1424">
@@ -27608,13 +27630,13 @@
         <v>49</v>
       </c>
       <c r="B1424" t="s" s="2">
+        <v>3099</v>
+      </c>
+      <c r="C1424" t="s" s="2">
+        <v>3100</v>
+      </c>
+      <c r="D1424" t="s" s="2">
         <v>3101</v>
-      </c>
-      <c r="C1424" t="s" s="2">
-        <v>3102</v>
-      </c>
-      <c r="D1424" t="s" s="2">
-        <v>3103</v>
       </c>
     </row>
     <row r="1425">
@@ -27622,13 +27644,13 @@
         <v>49</v>
       </c>
       <c r="B1425" t="s" s="2">
+        <v>3102</v>
+      </c>
+      <c r="C1425" t="s" s="2">
+        <v>3103</v>
+      </c>
+      <c r="D1425" t="s" s="2">
         <v>3104</v>
-      </c>
-      <c r="C1425" t="s" s="2">
-        <v>3105</v>
-      </c>
-      <c r="D1425" t="s" s="2">
-        <v>3106</v>
       </c>
     </row>
     <row r="1426">
@@ -27636,10 +27658,10 @@
         <v>49</v>
       </c>
       <c r="B1426" t="s" s="2">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="C1426" t="s" s="2">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="D1426" s="2"/>
     </row>
@@ -27648,13 +27670,13 @@
         <v>49</v>
       </c>
       <c r="B1427" t="s" s="2">
+        <v>3107</v>
+      </c>
+      <c r="C1427" t="s" s="2">
+        <v>3108</v>
+      </c>
+      <c r="D1427" t="s" s="2">
         <v>3109</v>
-      </c>
-      <c r="C1427" t="s" s="2">
-        <v>3110</v>
-      </c>
-      <c r="D1427" t="s" s="2">
-        <v>3111</v>
       </c>
     </row>
     <row r="1428">
@@ -27662,10 +27684,10 @@
         <v>49</v>
       </c>
       <c r="B1428" t="s" s="2">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="C1428" t="s" s="2">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="D1428" s="2"/>
     </row>
@@ -27674,10 +27696,10 @@
         <v>49</v>
       </c>
       <c r="B1429" t="s" s="2">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="C1429" t="s" s="2">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="D1429" s="2"/>
     </row>
@@ -27686,10 +27708,10 @@
         <v>49</v>
       </c>
       <c r="B1430" t="s" s="2">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="C1430" t="s" s="2">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="D1430" s="2"/>
     </row>
@@ -27698,10 +27720,10 @@
         <v>49</v>
       </c>
       <c r="B1431" t="s" s="2">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="C1431" t="s" s="2">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="D1431" s="2"/>
     </row>
@@ -27710,10 +27732,10 @@
         <v>49</v>
       </c>
       <c r="B1432" t="s" s="2">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="C1432" t="s" s="2">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="D1432" s="2"/>
     </row>
@@ -27722,10 +27744,10 @@
         <v>49</v>
       </c>
       <c r="B1433" t="s" s="2">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="C1433" t="s" s="2">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="D1433" s="2"/>
     </row>
@@ -27734,10 +27756,10 @@
         <v>49</v>
       </c>
       <c r="B1434" t="s" s="2">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="C1434" t="s" s="2">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="D1434" s="2"/>
     </row>
@@ -27746,10 +27768,10 @@
         <v>49</v>
       </c>
       <c r="B1435" t="s" s="2">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="C1435" t="s" s="2">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="D1435" s="2"/>
     </row>
@@ -27758,10 +27780,10 @@
         <v>49</v>
       </c>
       <c r="B1436" t="s" s="2">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="C1436" t="s" s="2">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="D1436" s="2"/>
     </row>
@@ -27770,10 +27792,10 @@
         <v>49</v>
       </c>
       <c r="B1437" t="s" s="2">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="C1437" t="s" s="2">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="D1437" s="2"/>
     </row>
@@ -27782,10 +27804,10 @@
         <v>49</v>
       </c>
       <c r="B1438" t="s" s="2">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="C1438" t="s" s="2">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="D1438" s="2"/>
     </row>
@@ -27794,10 +27816,10 @@
         <v>49</v>
       </c>
       <c r="B1439" t="s" s="2">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="C1439" t="s" s="2">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="D1439" s="2"/>
     </row>
@@ -27806,10 +27828,10 @@
         <v>49</v>
       </c>
       <c r="B1440" t="s" s="2">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="C1440" t="s" s="2">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="D1440" s="2"/>
     </row>
@@ -27818,10 +27840,10 @@
         <v>49</v>
       </c>
       <c r="B1441" t="s" s="2">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="C1441" t="s" s="2">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="D1441" s="2"/>
     </row>
@@ -27830,10 +27852,10 @@
         <v>49</v>
       </c>
       <c r="B1442" t="s" s="2">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="C1442" t="s" s="2">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="D1442" s="2"/>
     </row>
@@ -27842,10 +27864,10 @@
         <v>49</v>
       </c>
       <c r="B1443" t="s" s="2">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="C1443" t="s" s="2">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="D1443" s="2"/>
     </row>
@@ -27854,10 +27876,10 @@
         <v>49</v>
       </c>
       <c r="B1444" t="s" s="2">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="C1444" t="s" s="2">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="D1444" s="2"/>
     </row>
@@ -27866,10 +27888,10 @@
         <v>49</v>
       </c>
       <c r="B1445" t="s" s="2">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="C1445" t="s" s="2">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="D1445" s="2"/>
     </row>
@@ -27878,10 +27900,10 @@
         <v>49</v>
       </c>
       <c r="B1446" t="s" s="2">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="C1446" t="s" s="2">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="D1446" s="2"/>
     </row>
@@ -27890,10 +27912,10 @@
         <v>49</v>
       </c>
       <c r="B1447" t="s" s="2">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="C1447" t="s" s="2">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D1447" s="2"/>
     </row>
@@ -27902,10 +27924,10 @@
         <v>49</v>
       </c>
       <c r="B1448" t="s" s="2">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="C1448" t="s" s="2">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="D1448" s="2"/>
     </row>
@@ -27914,10 +27936,10 @@
         <v>49</v>
       </c>
       <c r="B1449" t="s" s="2">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="C1449" t="s" s="2">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="D1449" s="2"/>
     </row>
@@ -27926,10 +27948,10 @@
         <v>49</v>
       </c>
       <c r="B1450" t="s" s="2">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="C1450" t="s" s="2">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="D1450" s="2"/>
     </row>
@@ -27938,10 +27960,10 @@
         <v>49</v>
       </c>
       <c r="B1451" t="s" s="2">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="C1451" t="s" s="2">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="D1451" s="2"/>
     </row>
@@ -27950,10 +27972,10 @@
         <v>49</v>
       </c>
       <c r="B1452" t="s" s="2">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="C1452" t="s" s="2">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="D1452" s="2"/>
     </row>
@@ -27962,10 +27984,10 @@
         <v>49</v>
       </c>
       <c r="B1453" t="s" s="2">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="C1453" t="s" s="2">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="D1453" s="2"/>
     </row>
@@ -27974,10 +27996,10 @@
         <v>49</v>
       </c>
       <c r="B1454" t="s" s="2">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="C1454" t="s" s="2">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="D1454" s="2"/>
     </row>
@@ -27986,10 +28008,10 @@
         <v>49</v>
       </c>
       <c r="B1455" t="s" s="2">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="C1455" t="s" s="2">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="D1455" s="2"/>
     </row>
@@ -27998,10 +28020,10 @@
         <v>49</v>
       </c>
       <c r="B1456" t="s" s="2">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="C1456" t="s" s="2">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="D1456" s="2"/>
     </row>
@@ -28010,10 +28032,10 @@
         <v>49</v>
       </c>
       <c r="B1457" t="s" s="2">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="C1457" t="s" s="2">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="D1457" s="2"/>
     </row>
@@ -28022,10 +28044,10 @@
         <v>49</v>
       </c>
       <c r="B1458" t="s" s="2">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="C1458" t="s" s="2">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="D1458" s="2"/>
     </row>
@@ -28034,10 +28056,10 @@
         <v>49</v>
       </c>
       <c r="B1459" t="s" s="2">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="C1459" t="s" s="2">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="D1459" s="2"/>
     </row>
@@ -28046,10 +28068,10 @@
         <v>49</v>
       </c>
       <c r="B1460" t="s" s="2">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="C1460" t="s" s="2">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="D1460" s="2"/>
     </row>
@@ -28058,13 +28080,13 @@
         <v>49</v>
       </c>
       <c r="B1461" t="s" s="2">
+        <v>3176</v>
+      </c>
+      <c r="C1461" t="s" s="2">
+        <v>3177</v>
+      </c>
+      <c r="D1461" t="s" s="2">
         <v>3178</v>
-      </c>
-      <c r="C1461" t="s" s="2">
-        <v>3179</v>
-      </c>
-      <c r="D1461" t="s" s="2">
-        <v>3180</v>
       </c>
     </row>
     <row r="1462">
@@ -28072,10 +28094,10 @@
         <v>49</v>
       </c>
       <c r="B1462" t="s" s="2">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="C1462" t="s" s="2">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="D1462" s="2"/>
     </row>
@@ -28084,10 +28106,10 @@
         <v>49</v>
       </c>
       <c r="B1463" t="s" s="2">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="C1463" t="s" s="2">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="D1463" s="2"/>
     </row>
@@ -28096,10 +28118,10 @@
         <v>49</v>
       </c>
       <c r="B1464" t="s" s="2">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="C1464" t="s" s="2">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="D1464" s="2"/>
     </row>
@@ -28108,10 +28130,10 @@
         <v>49</v>
       </c>
       <c r="B1465" t="s" s="2">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="C1465" t="s" s="2">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="D1465" s="2"/>
     </row>
@@ -28120,10 +28142,10 @@
         <v>49</v>
       </c>
       <c r="B1466" t="s" s="2">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="C1466" t="s" s="2">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="D1466" s="2"/>
     </row>
@@ -28132,10 +28154,10 @@
         <v>49</v>
       </c>
       <c r="B1467" t="s" s="2">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="C1467" t="s" s="2">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="D1467" s="2"/>
     </row>
@@ -28144,10 +28166,10 @@
         <v>49</v>
       </c>
       <c r="B1468" t="s" s="2">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="C1468" t="s" s="2">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="D1468" s="2"/>
     </row>
@@ -28156,10 +28178,10 @@
         <v>49</v>
       </c>
       <c r="B1469" t="s" s="2">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="C1469" t="s" s="2">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="D1469" s="2"/>
     </row>
@@ -28168,10 +28190,10 @@
         <v>49</v>
       </c>
       <c r="B1470" t="s" s="2">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="C1470" t="s" s="2">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="D1470" s="2"/>
     </row>
@@ -28180,10 +28202,10 @@
         <v>49</v>
       </c>
       <c r="B1471" t="s" s="2">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="C1471" t="s" s="2">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="D1471" s="2"/>
     </row>
@@ -28192,10 +28214,10 @@
         <v>49</v>
       </c>
       <c r="B1472" t="s" s="2">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="C1472" t="s" s="2">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="D1472" s="2"/>
     </row>
@@ -28204,10 +28226,10 @@
         <v>49</v>
       </c>
       <c r="B1473" t="s" s="2">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="C1473" t="s" s="2">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="D1473" s="2"/>
     </row>
@@ -28216,10 +28238,10 @@
         <v>49</v>
       </c>
       <c r="B1474" t="s" s="2">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="C1474" t="s" s="2">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="D1474" s="2"/>
     </row>
@@ -28228,10 +28250,10 @@
         <v>49</v>
       </c>
       <c r="B1475" t="s" s="2">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="C1475" t="s" s="2">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="D1475" s="2"/>
     </row>
@@ -28240,10 +28262,10 @@
         <v>49</v>
       </c>
       <c r="B1476" t="s" s="2">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="C1476" t="s" s="2">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="D1476" s="2"/>
     </row>
@@ -28252,10 +28274,10 @@
         <v>49</v>
       </c>
       <c r="B1477" t="s" s="2">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="C1477" t="s" s="2">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="D1477" s="2"/>
     </row>
@@ -28264,10 +28286,10 @@
         <v>49</v>
       </c>
       <c r="B1478" t="s" s="2">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="C1478" t="s" s="2">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="D1478" s="2"/>
     </row>
@@ -28276,10 +28298,10 @@
         <v>49</v>
       </c>
       <c r="B1479" t="s" s="2">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="C1479" t="s" s="2">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="D1479" s="2"/>
     </row>
@@ -28288,10 +28310,10 @@
         <v>49</v>
       </c>
       <c r="B1480" t="s" s="2">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="C1480" t="s" s="2">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="D1480" s="2"/>
     </row>
@@ -28300,10 +28322,10 @@
         <v>49</v>
       </c>
       <c r="B1481" t="s" s="2">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="C1481" t="s" s="2">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="D1481" s="2"/>
     </row>
@@ -28312,12 +28334,72 @@
         <v>49</v>
       </c>
       <c r="B1482" t="s" s="2">
+        <v>3219</v>
+      </c>
+      <c r="C1482" t="s" s="2">
+        <v>3220</v>
+      </c>
+      <c r="D1482" s="2"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1483" t="s" s="2">
         <v>3221</v>
       </c>
-      <c r="C1482" t="s" s="2">
+      <c r="C1483" t="s" s="2">
         <v>3222</v>
       </c>
-      <c r="D1482" s="2"/>
+      <c r="D1483" s="2"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1484" t="s" s="2">
+        <v>3223</v>
+      </c>
+      <c r="C1484" t="s" s="2">
+        <v>3224</v>
+      </c>
+      <c r="D1484" s="2"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1485" t="s" s="2">
+        <v>3225</v>
+      </c>
+      <c r="C1485" t="s" s="2">
+        <v>3226</v>
+      </c>
+      <c r="D1485" s="2"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1486" t="s" s="2">
+        <v>3227</v>
+      </c>
+      <c r="C1486" t="s" s="2">
+        <v>3228</v>
+      </c>
+      <c r="D1486" s="2"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1487" t="s" s="2">
+        <v>3229</v>
+      </c>
+      <c r="C1487" t="s" s="2">
+        <v>3230</v>
+      </c>
+      <c r="D1487" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
